--- a/data/common_availability.xlsx
+++ b/data/common_availability.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Demo Lecturer 1</t>
+          <t>HEMA LATHA A/P KRISHNA NAIR</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Demo Lecturer 2</t>
+          <t>DR. JULIA BINTI JUREMI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -466,12 +466,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>01:00 PM - 02:00 PM</t>
+          <t>09:00 AM - 10:00 AM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -483,12 +483,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Demo Lecturer 1</t>
+          <t>HEMA LATHA A/P KRISHNA NAIR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Demo Lecturer 2</t>
+          <t>DR. JULIA BINTI JUREMI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -498,12 +498,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>02:00 PM - 03:00 PM</t>
+          <t>10:00 AM - 11:00 AM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -515,12 +515,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Demo Lecturer 1</t>
+          <t>HEMA LATHA A/P KRISHNA NAIR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Demo Lecturer 2</t>
+          <t>DR. JULIA BINTI JUREMI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -530,12 +530,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>03:00 PM - 04:00 PM</t>
+          <t>01:00 PM - 02:00 PM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -547,12 +547,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Demo Lecturer 1</t>
+          <t>HEMA LATHA A/P KRISHNA NAIR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Demo Lecturer 2</t>
+          <t>DR. JULIA BINTI JUREMI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -562,12 +562,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>04:00 PM - 05:00 PM</t>
+          <t>02:00 PM - 03:00 PM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -579,27 +579,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Demo Lecturer 1</t>
+          <t>HEMA LATHA A/P KRISHNA NAIR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Demo Lecturer 2</t>
+          <t>DR. JULIA BINTI JUREMI</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>04:00 PM - 05:00 PM</t>
+          <t>03:00 PM - 04:00 PM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -611,27 +611,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Demo Lecturer 1</t>
+          <t>HEMA LATHA A/P KRISHNA NAIR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Demo Lecturer 2</t>
+          <t>DR. JULIA BINTI JUREMI</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>09:00 AM - 10:00 AM</t>
+          <t>04:00 PM - 05:00 PM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -643,27 +643,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Demo Lecturer 1</t>
+          <t>HEMA LATHA A/P KRISHNA NAIR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Demo Lecturer 2</t>
+          <t>DR. JULIA BINTI JUREMI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10:00 AM - 11:00 AM</t>
+          <t>04:00 PM - 05:00 PM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -675,12 +675,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Demo Lecturer 1</t>
+          <t>HEMA LATHA A/P KRISHNA NAIR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Demo Lecturer 2</t>
+          <t>DR. JULIA BINTI JUREMI</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11:00 AM - 12:00 PM</t>
+          <t>09:00 AM - 10:00 AM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -707,12 +707,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Demo Lecturer 1</t>
+          <t>HEMA LATHA A/P KRISHNA NAIR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Demo Lecturer 2</t>
+          <t>DR. JULIA BINTI JUREMI</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12:00 PM - 01:00 PM</t>
+          <t>10:00 AM - 11:00 AM</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -739,12 +739,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Demo Lecturer 1</t>
+          <t>HEMA LATHA A/P KRISHNA NAIR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Demo Lecturer 2</t>
+          <t>DR. JULIA BINTI JUREMI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -754,12 +754,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>01:00 PM - 02:00 PM</t>
+          <t>11:00 AM - 12:00 PM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -771,12 +771,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Demo Lecturer 1</t>
+          <t>HEMA LATHA A/P KRISHNA NAIR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Demo Lecturer 2</t>
+          <t>DR. JULIA BINTI JUREMI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>04:00 PM - 05:00 PM</t>
+          <t>12:00 PM - 01:00 PM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -803,27 +803,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Demo Lecturer 1</t>
+          <t>HEMA LATHA A/P KRISHNA NAIR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Demo Lecturer 2</t>
+          <t>DR. JULIA BINTI JUREMI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11:00 AM - 12:00 PM</t>
+          <t>04:00 PM - 05:00 PM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -835,12 +835,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Demo Lecturer 1</t>
+          <t>HEMA LATHA A/P KRISHNA NAIR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Demo Lecturer 2</t>
+          <t>DR. JULIA BINTI JUREMI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -850,12 +850,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12:00 PM - 01:00 PM</t>
+          <t>09:00 AM - 10:00 AM</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -867,12 +867,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Demo Lecturer 1</t>
+          <t>HEMA LATHA A/P KRISHNA NAIR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Demo Lecturer 2</t>
+          <t>DR. JULIA BINTI JUREMI</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -882,12 +882,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>01:00 PM - 02:00 PM</t>
+          <t>10:00 AM - 11:00 AM</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -899,12 +899,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Demo Lecturer 1</t>
+          <t>HEMA LATHA A/P KRISHNA NAIR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Demo Lecturer 2</t>
+          <t>DR. JULIA BINTI JUREMI</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>02:00 PM - 03:00 PM</t>
+          <t>11:00 AM - 12:00 PM</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -931,12 +931,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Demo Lecturer 1</t>
+          <t>HEMA LATHA A/P KRISHNA NAIR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Demo Lecturer 2</t>
+          <t>DR. JULIA BINTI JUREMI</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>03:00 PM - 04:00 PM</t>
+          <t>12:00 PM - 01:00 PM</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -963,12 +963,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Demo Lecturer 1</t>
+          <t>HEMA LATHA A/P KRISHNA NAIR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Demo Lecturer 2</t>
+          <t>DR. JULIA BINTI JUREMI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>04:00 PM - 05:00 PM</t>
+          <t>01:00 PM - 02:00 PM</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -995,27 +995,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Demo Lecturer 1</t>
+          <t>HEMA LATHA A/P KRISHNA NAIR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Demo Lecturer 2</t>
+          <t>DR. JULIA BINTI JUREMI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12:00 PM - 01:00 PM</t>
+          <t>02:00 PM - 03:00 PM</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1027,27 +1027,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Demo Lecturer 1</t>
+          <t>HEMA LATHA A/P KRISHNA NAIR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Demo Lecturer 2</t>
+          <t>DR. JULIA BINTI JUREMI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>01:00 PM - 02:00 PM</t>
+          <t>03:00 PM - 04:00 PM</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1059,27 +1059,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Demo Lecturer 3</t>
+          <t>HEMA LATHA A/P KRISHNA NAIR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Demo Lecturer 1</t>
+          <t>DR. JULIA BINTI JUREMI</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>11:00 AM - 12:00 PM</t>
+          <t>04:00 PM - 05:00 PM</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1091,27 +1091,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Demo Lecturer 3</t>
+          <t>HEMA LATHA A/P KRISHNA NAIR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Demo Lecturer 1</t>
+          <t>DR. JULIA BINTI JUREMI</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>12:00 PM - 01:00 PM</t>
+          <t>09:00 AM - 10:00 AM</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1123,27 +1123,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Demo Lecturer 3</t>
+          <t>HEMA LATHA A/P KRISHNA NAIR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Demo Lecturer 1</t>
+          <t>DR. JULIA BINTI JUREMI</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>01:00 PM - 02:00 PM</t>
+          <t>10:00 AM - 11:00 AM</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1155,27 +1155,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Demo Lecturer 3</t>
+          <t>HEMA LATHA A/P KRISHNA NAIR</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Demo Lecturer 1</t>
+          <t>DR. JULIA BINTI JUREMI</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>02:00 PM - 03:00 PM</t>
+          <t>11:00 AM - 12:00 PM</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1187,27 +1187,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Demo Lecturer 3</t>
+          <t>HEMA LATHA A/P KRISHNA NAIR</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Demo Lecturer 1</t>
+          <t>DR. JULIA BINTI JUREMI</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>03:00 PM - 04:00 PM</t>
+          <t>12:00 PM - 01:00 PM</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1219,574 +1219,30 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Demo Lecturer 3</t>
+          <t>HEMA LATHA A/P KRISHNA NAIR</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Demo Lecturer 1</t>
+          <t>DR. JULIA BINTI JUREMI</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>04:00 PM - 05:00 PM</t>
+          <t>01:00 PM - 02:00 PM</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 3</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 1</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>04:00 PM - 05:00 PM</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 3</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 1</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>09:00 AM - 10:00 AM</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 3</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 1</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>10:00 AM - 11:00 AM</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 3</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 1</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>11:00 AM - 12:00 PM</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 3</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 1</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>12:00 PM - 01:00 PM</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 3</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 1</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>01:00 PM - 02:00 PM</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 3</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 1</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>04:00 PM - 05:00 PM</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 3</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 1</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>09:00 AM - 10:00 AM</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 3</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 1</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>10:00 AM - 11:00 AM</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 3</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 1</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>11:00 AM - 12:00 PM</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 3</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 1</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>12:00 PM - 01:00 PM</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 3</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 1</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>01:00 PM - 02:00 PM</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 3</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 1</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>09:00 AM - 10:00 AM</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 3</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 1</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>10:00 AM - 11:00 AM</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 3</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 1</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>11:00 AM - 12:00 PM</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 3</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 1</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>12:00 PM - 01:00 PM</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 3</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 1</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>01:00 PM - 02:00 PM</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
